--- a/outputs/formato_input_catalog_control_center_top_bottom_20260720.xlsx
+++ b/outputs/formato_input_catalog_control_center_top_bottom_20260720.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT_COMERCIAL" sheetId="1" r:id="R1d5e45306d944a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICCIONARIO_COLUMNAS" sheetId="2" r:id="R2b49714f67a94d2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIPOS_PRENDA" sheetId="3" r:id="R08b199c1dc0c4628"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIAS_TALLA" sheetId="4" r:id="R29abed733301415e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORIAS" sheetId="5" r:id="R9932a7771e9842fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES_PERMITIDOS" sheetId="6" r:id="R15c01aeed0bf4140"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_Y_ADVERTENCIAS" sheetId="7" r:id="R4c074ce3d2ac44d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT_COMERCIAL" sheetId="1" r:id="R15fa54c0229c4877"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICCIONARIO_COLUMNAS" sheetId="2" r:id="R0eab6cb5a6504ff1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIPOS_PRENDA" sheetId="3" r:id="R1619eedf11de4e2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIAS_TALLA" sheetId="4" r:id="R85846c64e5b7428f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORIAS" sheetId="5" r:id="R56b7bbc6f1e449cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES_PERMITIDOS" sheetId="6" r:id="R5940708400f7478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_Y_ADVERTENCIAS" sheetId="7" r:id="Rd58c459bd7ca4f9f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,8 +367,8 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="29.1299991607666" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="50.5" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="50.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13.380000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="11.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="24.3799991607666" hidden="0" customWidth="1"/>
@@ -381,17 +381,17 @@
     <x:col min="13" max="13" width="27.5" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="20.75" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="24.5" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="57" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="48.630001068115234" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="36.25" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="62.25" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="38.25" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="31.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="17" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="28" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="13.5" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="9.25" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="16.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="19.6299991607666" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="18.6299991607666" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="23" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="43.25" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="56.630001068115234" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="59" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="23.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="27.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="38.25" hidden="0" customWidth="1"/>
     <x:col min="27" max="27" width="15.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="28" max="28" width="19.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="16.1299991607666" hidden="0" customWidth="1"/>
@@ -563,7 +563,7 @@
         <x:v>Columbia, Vestuario, Mujer, Casacas</x:v>
       </x:c>
       <x:c r="Z2" s="8" t="str">
-        <x:v>casacas-mujer-columbia-2092991-nry</x:v>
+        <x:v>casaca-impermeable-mujer-arcadia-ii-2092991-nry</x:v>
       </x:c>
       <x:c r="AA2" s="8" t="str"/>
       <x:c r="AB2" s="8" t="str"/>
@@ -577,10 +577,10 @@
         <x:v>Codigo modelo-color. Ej: 2092991-NRY</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
+        <x:v>Modelo sin color.</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
+        <x:v>Codigo de color fuente.</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
         <x:v>Marca destino.</x:v>
@@ -619,22 +619,22 @@
         <x:v>Instrucciones de cuidado.</x:v>
       </x:c>
       <x:c r="P3" s="9" t="str">
-        <x:v>La app la obtiene desde BigQuery/ARTI. No inventar ni cargar tallas teoricas.</x:v>
+        <x:v>Talla real. No inventar.</x:v>
       </x:c>
       <x:c r="Q3" s="9" t="str">
-        <x:v>La app lo obtiene desde BigQuery/ARTI. Obligatorio por variante.</x:v>
+        <x:v>Cod Int/SKU obligatorio por variante.</x:v>
       </x:c>
       <x:c r="R3" s="9" t="str">
-        <x:v>La app lo obtiene desde BigQuery/ARTI si existe.</x:v>
+        <x:v>Codigo de barras.</x:v>
       </x:c>
       <x:c r="S3" s="9" t="str">
-        <x:v>La app lo obtiene desde Shopify/ARTI si existe; la marca solo completa si se solicita.</x:v>
+        <x:v>Precio final.</x:v>
       </x:c>
       <x:c r="T3" s="9" t="str">
-        <x:v>Precio antes si aplica desde fuente comercial/ARTI.</x:v>
+        <x:v>Precio antes si aplica.</x:v>
       </x:c>
       <x:c r="U3" s="9" t="str">
-        <x:v>Stock eComm referencial desde BigQuery.</x:v>
+        <x:v>Stock eComm referencial.</x:v>
       </x:c>
       <x:c r="V3" s="9" t="str">
         <x:v>Separar por coma.</x:v>
@@ -643,13 +643,13 @@
         <x:v>Nombre o GID de metaobjeto.</x:v>
       </x:c>
       <x:c r="X3" s="9" t="str">
-        <x:v>La app la resuelve por categoria, tipo de prenda y genero.</x:v>
+        <x:v>Guia Shopify si viene aprobada.</x:v>
       </x:c>
       <x:c r="Y3" s="9" t="str">
-        <x:v>La app los sugiere con marca, categoria, genero, tipo, tecnologia y Mod-Col.</x:v>
+        <x:v>Tags separados por coma.</x:v>
       </x:c>
       <x:c r="Z3" s="9" t="str">
-        <x:v>No llenar manualmente. Formula: tipo de prenda + genero + marca + Mod-Col.</x:v>
+        <x:v>Handle sugerido.</x:v>
       </x:c>
       <x:c r="AA3" s="9" t="str">
         <x:v>Titulo SEO opcional.</x:v>
@@ -2189,10 +2189,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22.5" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="9.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="62.25" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="33.630001068115234" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="29.1299991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38.25" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14.5" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="23.6299991607666" hidden="0" customWidth="1"/>
   </x:cols>
@@ -2248,13 +2248,13 @@
         <x:v>Codigo modelo</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Identificacion</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
+        <x:v>Modelo sin color.</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
         <x:v>2092991</x:v>
@@ -2271,13 +2271,13 @@
         <x:v>Codigo color</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Identificacion</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
+        <x:v>Codigo de color fuente.</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
         <x:v>NRY</x:v>
@@ -2568,13 +2568,13 @@
         <x:v>Talla</x:v>
       </x:c>
       <x:c r="B17" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Variantes y tallas</x:v>
       </x:c>
       <x:c r="C17" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D17" s="13" t="str">
-        <x:v>La app la obtiene desde BigQuery/ARTI. No inventar ni cargar tallas teoricas.</x:v>
+        <x:v>Talla real. No inventar.</x:v>
       </x:c>
       <x:c r="E17" s="13" t="str">
         <x:v>M</x:v>
@@ -2591,13 +2591,13 @@
         <x:v>SKU</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Variantes y tallas</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D18" s="13" t="str">
-        <x:v>La app lo obtiene desde BigQuery/ARTI. Obligatorio por variante.</x:v>
+        <x:v>Cod Int/SKU obligatorio por variante.</x:v>
       </x:c>
       <x:c r="E18" s="13" t="str">
         <x:v>5327440</x:v>
@@ -2614,13 +2614,13 @@
         <x:v>EAN</x:v>
       </x:c>
       <x:c r="B19" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Variantes y tallas</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D19" s="13" t="str">
-        <x:v>La app lo obtiene desde BigQuery/ARTI si existe.</x:v>
+        <x:v>Codigo de barras.</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
         <x:v>7800000000000</x:v>
@@ -2637,13 +2637,13 @@
         <x:v>Precio</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Precios</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D20" s="13" t="str">
-        <x:v>La app lo obtiene desde Shopify/ARTI si existe; la marca solo completa si se solicita.</x:v>
+        <x:v>Precio final.</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
         <x:v>299.90</x:v>
@@ -2660,13 +2660,13 @@
         <x:v>Compare At Price</x:v>
       </x:c>
       <x:c r="B21" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Precios</x:v>
       </x:c>
       <x:c r="C21" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D21" s="13" t="str">
-        <x:v>Precio antes si aplica desde fuente comercial/ARTI.</x:v>
+        <x:v>Precio antes si aplica.</x:v>
       </x:c>
       <x:c r="E21" s="13" t="str"/>
       <x:c r="F21" s="13" t="str">
@@ -2681,13 +2681,13 @@
         <x:v>Stock disponible</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Inventario</x:v>
       </x:c>
       <x:c r="C22" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D22" s="13" t="str">
-        <x:v>Stock eComm referencial desde BigQuery.</x:v>
+        <x:v>Stock eComm referencial.</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
         <x:v>12</x:v>
@@ -2750,13 +2750,13 @@
         <x:v>Guia de tallas</x:v>
       </x:c>
       <x:c r="B25" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>Guia de talla</x:v>
       </x:c>
       <x:c r="C25" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D25" s="13" t="str">
-        <x:v>La app la resuelve por categoria, tipo de prenda y genero.</x:v>
+        <x:v>Guia Shopify si viene aprobada.</x:v>
       </x:c>
       <x:c r="E25" s="13" t="str">
         <x:v>CLB_MUJER_TOPS</x:v>
@@ -2773,13 +2773,13 @@
         <x:v>Tags sugeridos</x:v>
       </x:c>
       <x:c r="B26" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>SEO y tags</x:v>
       </x:c>
       <x:c r="C26" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D26" s="13" t="str">
-        <x:v>La app los sugiere con marca, categoria, genero, tipo, tecnologia y Mod-Col.</x:v>
+        <x:v>Tags separados por coma.</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
         <x:v>Columbia, Vestuario, Mujer, Casacas</x:v>
@@ -2796,16 +2796,16 @@
         <x:v>Handle sugerido</x:v>
       </x:c>
       <x:c r="B27" s="13" t="str">
-        <x:v>Campo tecnico autogenerado</x:v>
+        <x:v>SEO y tags</x:v>
       </x:c>
       <x:c r="C27" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D27" s="13" t="str">
-        <x:v>No llenar manualmente. Formula: tipo de prenda + genero + marca + Mod-Col.</x:v>
+        <x:v>Handle sugerido.</x:v>
       </x:c>
       <x:c r="E27" s="13" t="str">
-        <x:v>casacas-mujer-columbia-2092991-nry</x:v>
+        <x:v>casaca-impermeable-mujer-arcadia-ii-2092991-nry</x:v>
       </x:c>
       <x:c r="F27" s="13" t="str">
         <x:v>Producto / reporte</x:v>

--- a/outputs/formato_input_catalog_control_center_top_bottom_20260720.xlsx
+++ b/outputs/formato_input_catalog_control_center_top_bottom_20260720.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT_COMERCIAL" sheetId="1" r:id="R15fa54c0229c4877"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICCIONARIO_COLUMNAS" sheetId="2" r:id="R0eab6cb5a6504ff1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIPOS_PRENDA" sheetId="3" r:id="R1619eedf11de4e2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIAS_TALLA" sheetId="4" r:id="R85846c64e5b7428f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORIAS" sheetId="5" r:id="R56b7bbc6f1e449cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES_PERMITIDOS" sheetId="6" r:id="R5940708400f7478e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_Y_ADVERTENCIAS" sheetId="7" r:id="Rd58c459bd7ca4f9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPUT_COMERCIAL" sheetId="1" r:id="R1d5e45306d944a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DICCIONARIO_COLUMNAS" sheetId="2" r:id="R2b49714f67a94d2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TIPOS_PRENDA" sheetId="3" r:id="R08b199c1dc0c4628"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GUIAS_TALLA" sheetId="4" r:id="R29abed733301415e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CATEGORIAS" sheetId="5" r:id="R9932a7771e9842fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALORES_PERMITIDOS" sheetId="6" r:id="R15c01aeed0bf4140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ERRORES_Y_ADVERTENCIAS" sheetId="7" r:id="R4c074ce3d2ac44d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -367,8 +367,8 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="29.1299991607666" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="17.8799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="50.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="50.5" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="11.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="26.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="24.3799991607666" hidden="0" customWidth="1"/>
@@ -381,17 +381,17 @@
     <x:col min="13" max="13" width="27.5" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="20.75" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="24.5" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="17" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="28" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="13.5" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="9.25" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="16.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="21" max="21" width="19.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="57" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="48.630001068115234" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="36.25" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="62.25" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="38.25" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="31.6299991607666" hidden="0" customWidth="1"/>
     <x:col min="22" max="22" width="18.6299991607666" hidden="0" customWidth="1"/>
     <x:col min="23" max="23" width="23" hidden="0" customWidth="1"/>
-    <x:col min="24" max="24" width="23.8799991607666" hidden="0" customWidth="1"/>
-    <x:col min="25" max="25" width="27.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="26" max="26" width="38.25" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="43.25" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="56.630001068115234" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="59" hidden="0" customWidth="1"/>
     <x:col min="27" max="27" width="15.380000114440918" hidden="0" customWidth="1"/>
     <x:col min="28" max="28" width="19.8799991607666" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="16.1299991607666" hidden="0" customWidth="1"/>
@@ -563,7 +563,7 @@
         <x:v>Columbia, Vestuario, Mujer, Casacas</x:v>
       </x:c>
       <x:c r="Z2" s="8" t="str">
-        <x:v>casaca-impermeable-mujer-arcadia-ii-2092991-nry</x:v>
+        <x:v>casacas-mujer-columbia-2092991-nry</x:v>
       </x:c>
       <x:c r="AA2" s="8" t="str"/>
       <x:c r="AB2" s="8" t="str"/>
@@ -577,10 +577,10 @@
         <x:v>Codigo modelo-color. Ej: 2092991-NRY</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>Modelo sin color.</x:v>
+        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>Codigo de color fuente.</x:v>
+        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
         <x:v>Marca destino.</x:v>
@@ -619,22 +619,22 @@
         <x:v>Instrucciones de cuidado.</x:v>
       </x:c>
       <x:c r="P3" s="9" t="str">
-        <x:v>Talla real. No inventar.</x:v>
+        <x:v>La app la obtiene desde BigQuery/ARTI. No inventar ni cargar tallas teoricas.</x:v>
       </x:c>
       <x:c r="Q3" s="9" t="str">
-        <x:v>Cod Int/SKU obligatorio por variante.</x:v>
+        <x:v>La app lo obtiene desde BigQuery/ARTI. Obligatorio por variante.</x:v>
       </x:c>
       <x:c r="R3" s="9" t="str">
-        <x:v>Codigo de barras.</x:v>
+        <x:v>La app lo obtiene desde BigQuery/ARTI si existe.</x:v>
       </x:c>
       <x:c r="S3" s="9" t="str">
-        <x:v>Precio final.</x:v>
+        <x:v>La app lo obtiene desde Shopify/ARTI si existe; la marca solo completa si se solicita.</x:v>
       </x:c>
       <x:c r="T3" s="9" t="str">
-        <x:v>Precio antes si aplica.</x:v>
+        <x:v>Precio antes si aplica desde fuente comercial/ARTI.</x:v>
       </x:c>
       <x:c r="U3" s="9" t="str">
-        <x:v>Stock eComm referencial.</x:v>
+        <x:v>Stock eComm referencial desde BigQuery.</x:v>
       </x:c>
       <x:c r="V3" s="9" t="str">
         <x:v>Separar por coma.</x:v>
@@ -643,13 +643,13 @@
         <x:v>Nombre o GID de metaobjeto.</x:v>
       </x:c>
       <x:c r="X3" s="9" t="str">
-        <x:v>Guia Shopify si viene aprobada.</x:v>
+        <x:v>La app la resuelve por categoria, tipo de prenda y genero.</x:v>
       </x:c>
       <x:c r="Y3" s="9" t="str">
-        <x:v>Tags separados por coma.</x:v>
+        <x:v>La app los sugiere con marca, categoria, genero, tipo, tecnologia y Mod-Col.</x:v>
       </x:c>
       <x:c r="Z3" s="9" t="str">
-        <x:v>Handle sugerido.</x:v>
+        <x:v>No llenar manualmente. Formula: tipo de prenda + genero + marca + Mod-Col.</x:v>
       </x:c>
       <x:c r="AA3" s="9" t="str">
         <x:v>Titulo SEO opcional.</x:v>
@@ -2189,10 +2189,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="13.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="9.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="29.1299991607666" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="38.25" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="62.25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="33.630001068115234" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="14.5" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="23.6299991607666" hidden="0" customWidth="1"/>
   </x:cols>
@@ -2248,13 +2248,13 @@
         <x:v>Codigo modelo</x:v>
       </x:c>
       <x:c r="B3" s="13" t="str">
-        <x:v>Identificacion</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C3" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D3" s="13" t="str">
-        <x:v>Modelo sin color.</x:v>
+        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
       </x:c>
       <x:c r="E3" s="13" t="str">
         <x:v>2092991</x:v>
@@ -2271,13 +2271,13 @@
         <x:v>Codigo color</x:v>
       </x:c>
       <x:c r="B4" s="13" t="str">
-        <x:v>Identificacion</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C4" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D4" s="13" t="str">
-        <x:v>Codigo de color fuente.</x:v>
+        <x:v>La app lo puede obtener desde Mod-Col/ARTI. No lo llena la marca.</x:v>
       </x:c>
       <x:c r="E4" s="13" t="str">
         <x:v>NRY</x:v>
@@ -2568,13 +2568,13 @@
         <x:v>Talla</x:v>
       </x:c>
       <x:c r="B17" s="13" t="str">
-        <x:v>Variantes y tallas</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C17" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D17" s="13" t="str">
-        <x:v>Talla real. No inventar.</x:v>
+        <x:v>La app la obtiene desde BigQuery/ARTI. No inventar ni cargar tallas teoricas.</x:v>
       </x:c>
       <x:c r="E17" s="13" t="str">
         <x:v>M</x:v>
@@ -2591,13 +2591,13 @@
         <x:v>SKU</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>Variantes y tallas</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D18" s="13" t="str">
-        <x:v>Cod Int/SKU obligatorio por variante.</x:v>
+        <x:v>La app lo obtiene desde BigQuery/ARTI. Obligatorio por variante.</x:v>
       </x:c>
       <x:c r="E18" s="13" t="str">
         <x:v>5327440</x:v>
@@ -2614,13 +2614,13 @@
         <x:v>EAN</x:v>
       </x:c>
       <x:c r="B19" s="13" t="str">
-        <x:v>Variantes y tallas</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D19" s="13" t="str">
-        <x:v>Codigo de barras.</x:v>
+        <x:v>La app lo obtiene desde BigQuery/ARTI si existe.</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
         <x:v>7800000000000</x:v>
@@ -2637,13 +2637,13 @@
         <x:v>Precio</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>Precios</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
         <x:v>SI</x:v>
       </x:c>
       <x:c r="D20" s="13" t="str">
-        <x:v>Precio final.</x:v>
+        <x:v>La app lo obtiene desde Shopify/ARTI si existe; la marca solo completa si se solicita.</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
         <x:v>299.90</x:v>
@@ -2660,13 +2660,13 @@
         <x:v>Compare At Price</x:v>
       </x:c>
       <x:c r="B21" s="13" t="str">
-        <x:v>Precios</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C21" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D21" s="13" t="str">
-        <x:v>Precio antes si aplica.</x:v>
+        <x:v>Precio antes si aplica desde fuente comercial/ARTI.</x:v>
       </x:c>
       <x:c r="E21" s="13" t="str"/>
       <x:c r="F21" s="13" t="str">
@@ -2681,13 +2681,13 @@
         <x:v>Stock disponible</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
-        <x:v>Inventario</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C22" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D22" s="13" t="str">
-        <x:v>Stock eComm referencial.</x:v>
+        <x:v>Stock eComm referencial desde BigQuery.</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
         <x:v>12</x:v>
@@ -2750,13 +2750,13 @@
         <x:v>Guia de tallas</x:v>
       </x:c>
       <x:c r="B25" s="13" t="str">
-        <x:v>Guia de talla</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C25" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D25" s="13" t="str">
-        <x:v>Guia Shopify si viene aprobada.</x:v>
+        <x:v>La app la resuelve por categoria, tipo de prenda y genero.</x:v>
       </x:c>
       <x:c r="E25" s="13" t="str">
         <x:v>CLB_MUJER_TOPS</x:v>
@@ -2773,13 +2773,13 @@
         <x:v>Tags sugeridos</x:v>
       </x:c>
       <x:c r="B26" s="13" t="str">
-        <x:v>SEO y tags</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C26" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D26" s="13" t="str">
-        <x:v>Tags separados por coma.</x:v>
+        <x:v>La app los sugiere con marca, categoria, genero, tipo, tecnologia y Mod-Col.</x:v>
       </x:c>
       <x:c r="E26" s="13" t="str">
         <x:v>Columbia, Vestuario, Mujer, Casacas</x:v>
@@ -2796,16 +2796,16 @@
         <x:v>Handle sugerido</x:v>
       </x:c>
       <x:c r="B27" s="13" t="str">
-        <x:v>SEO y tags</x:v>
+        <x:v>Campo tecnico autogenerado</x:v>
       </x:c>
       <x:c r="C27" s="13" t="str">
         <x:v>NO</x:v>
       </x:c>
       <x:c r="D27" s="13" t="str">
-        <x:v>Handle sugerido.</x:v>
+        <x:v>No llenar manualmente. Formula: tipo de prenda + genero + marca + Mod-Col.</x:v>
       </x:c>
       <x:c r="E27" s="13" t="str">
-        <x:v>casaca-impermeable-mujer-arcadia-ii-2092991-nry</x:v>
+        <x:v>casacas-mujer-columbia-2092991-nry</x:v>
       </x:c>
       <x:c r="F27" s="13" t="str">
         <x:v>Producto / reporte</x:v>
